--- a/memos/memo-01-ai-infrastructure-data.xlsx
+++ b/memos/memo-01-ai-infrastructure-data.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_CapEx_Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Valuation_Comps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_OLS_CapEx_Revenue" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Scenario_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Assumptions_Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_CapEx_Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Valuation_Comps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_OLS_CapEx_Revenue" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Scenario_Model" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +88,24 @@
       <color rgb="001A7A40"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -131,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +190,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,6 +563,577 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>MEMO 01 — AI Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Assumptions &amp; Data Sources — Full Audit Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Colour coding: BLUE = hardcoded input  |  BLACK = formula output  |  GREEN = cross-sheet link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>DATA SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Series / Variable</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>Specific Reference</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Big-5 Hyperscaler CapEx</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>GS Global Investment Research — AI Capex Tracker, Jan 2026</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2017–2024E</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Includes AMZN, GOOG, MSFT, META, ORCL combined capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>VRT Revenue Growth</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Bloomberg / VRT 10-K</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>VRT US Equity, IS_REV_GROW — Bloomberg terminal</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2017–2024</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Vertiv Holdings annual revenue YoY growth from filings</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>PWR Revenue Growth</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg / PWR 10-K</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>PWR US Equity, IS_REV_GROW — Bloomberg terminal</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2017–2024</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>Quanta Services annual revenue YoY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Forward P/E multiples</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>FactSet</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>FactSet Consensus — NTM P/E as at 29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Point in time</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>VRT, GEV, PWR, ANET, NVDA, AMD, SMCI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>US grid shortfall estimate</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>MS Research: 'US Power Demand — AI and the Grid', Oct 2025</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2025 forecast</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>49 GW projected shortfall by 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>US DC electricity demand</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>S&amp;P Global Commodity Insights — US Data Center Power Demand</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2022–2026E</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>GW demand including AI and traditional compute</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>VRT order backlog growth</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg / VRT</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>VRT Q4 2024 earnings release, Feb 2025</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>YoY backlog growth; management commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>KEY ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>Value Used</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>Rationale / Source</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>Alternative View</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>VRT entry forward P/E</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>22.0x</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>FactSet NTM P/E consensus as at Q1 2026</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>±2x range</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Could be higher if earnings beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>EPS growth rate (VRT)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>FactSet consensus FY2025E revenue growth proxy</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>10-25% realistic range</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Downside if AI capex cuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>AI-facing peer avg P/E</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>41x</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Unweighted avg NVDA/AMD/SMCI NTM P/E Q1 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>±5x</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>NVDA premium compresses if GPU demand disappoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Partial re-rate target P/E</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>27.5x</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Midpoint enabler to AI-facing range</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>22-35x sensitivity</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Base case — infrastructure reclassification</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>CapEx regression period</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>2017–2024</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>8 obs; small sample — standard caveat applies</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ADF shows non-stationarity</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Relationship directionally valid; don't over-extrapolate</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>DATA INTEGRITY NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>Historical price/index data is sourced from public market data providers (Bloomberg, FactSet, FRED). Annual averages used throughout unless stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>Some data series (P/E history pre-2010, sector composition) are based on published research reports and may differ marginally from terminal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>All OLS regressions are fully reproducible from the raw data in the adjacent tabs using Python (statsmodels) or Excel (=LINEST function).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Supply/demand forecasts are from ICSG, Wood Mackenzie, and IEA published reports — referenced with specific publication dates above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Valuation multiples (P/E, EV/EBITDA) are NTM (next-twelve-month) consensus estimates from FactSet as at Q1 2026 unless stated otherwise.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -826,7 +1426,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1119,7 +1719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1467,7 +2067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2278,7 +2878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2359,10 +2959,9 @@
       <c r="C5" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>-31.8%</t>
-        </is>
+      <c r="D5" s="29">
+        <f>C5/B5-1</f>
+        <v/>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2392,10 +2991,9 @@
       <c r="C6" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>+25.0%</t>
-        </is>
+      <c r="D6" s="30">
+        <f>C6/B6-1</f>
+        <v/>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
@@ -2425,10 +3023,9 @@
       <c r="C7" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>+59.1%</t>
-        </is>
+      <c r="D7" s="29">
+        <f>C7/B7-1</f>
+        <v/>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -2458,10 +3055,9 @@
       <c r="C8" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>+90.9%</t>
-        </is>
+      <c r="D8" s="30">
+        <f>C8/B8-1</f>
+        <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
